--- a/TestData/LV_T2006_GiftLog_GiftRequestProcess_GiftSubmissionForCurrentAndNextCalendarYear.xlsx
+++ b/TestData/LV_T2006_GiftLog_GiftRequestProcess_GiftSubmissionForCurrentAndNextCalendarYear.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85FDA064-0FE7-4D48-BD6E-08DD56DDE21B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D22C9BB-E2F6-4CF2-B9BD-57FE11A5A280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="5" r:id="rId1"/>
@@ -74,9 +74,6 @@
     <t>ContactName</t>
   </si>
   <si>
-    <t>Test External</t>
-  </si>
-  <si>
     <t>CongratulationsMsg</t>
   </si>
   <si>
@@ -128,9 +125,6 @@
     <t>Success:\r\nYour Gift has been updated.</t>
   </si>
   <si>
-    <t>Giorgia Cardia</t>
-  </si>
-  <si>
     <t>StandardTestCompany</t>
   </si>
   <si>
@@ -147,6 +141,12 @@
   </si>
   <si>
     <t>Error:Desired Date Should not be greater than one Year.</t>
+  </si>
+  <si>
+    <t>Olivia Ricketts</t>
+  </si>
+  <si>
+    <t>Giftlog Contact</t>
   </si>
 </sst>
 </file>
@@ -485,12 +485,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -506,12 +506,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -529,12 +529,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -566,7 +566,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>5</v>
@@ -575,7 +575,7 @@
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>8</v>
@@ -593,13 +593,13 @@
         <v>1</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -607,7 +607,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>4</v>
@@ -616,7 +616,7 @@
         <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
@@ -625,22 +625,22 @@
         <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="J2" t="s">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -672,7 +672,7 @@
         <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
@@ -684,36 +684,36 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
         <v>26</v>
       </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>27</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -732,12 +732,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T2006_GiftLog_GiftRequestProcess_GiftSubmissionForCurrentAndNextCalendarYear.xlsx
+++ b/TestData/LV_T2006_GiftLog_GiftRequestProcess_GiftSubmissionForCurrentAndNextCalendarYear.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D22C9BB-E2F6-4CF2-B9BD-57FE11A5A280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{978DA9EA-EEE7-41C8-85EC-9016ED4E40B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="5" r:id="rId1"/>
@@ -143,10 +143,10 @@
     <t>Error:Desired Date Should not be greater than one Year.</t>
   </si>
   <si>
-    <t>Olivia Ricketts</t>
-  </si>
-  <si>
     <t>Giftlog Contact</t>
+  </si>
+  <si>
+    <t>Melissa Zatta</t>
   </si>
 </sst>
 </file>
@@ -190,11 +190,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -489,8 +492,8 @@
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>37</v>
+      <c r="A2" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -548,7 +551,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.109375" customWidth="1"/>
     <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -606,8 +609,8 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>37</v>
+      <c r="B2" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>4</v>
@@ -628,7 +631,7 @@
         <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J2" t="s">
         <v>0</v>

--- a/TestData/LV_T2006_GiftLog_GiftRequestProcess_GiftSubmissionForCurrentAndNextCalendarYear.xlsx
+++ b/TestData/LV_T2006_GiftLog_GiftRequestProcess_GiftSubmissionForCurrentAndNextCalendarYear.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{978DA9EA-EEE7-41C8-85EC-9016ED4E40B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23CD10C3-0370-4E75-B851-07B1EBD1AB9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="5" r:id="rId1"/>
@@ -481,17 +481,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>38</v>
       </c>
@@ -505,14 +505,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3994E973-1708-4FB5-8060-8F9C8F324766}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -525,17 +525,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64FBBFAF-DD7C-4A76-8E39-94296D365B50}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -548,23 +548,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.109375" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -605,7 +605,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -655,19 +655,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.21875" customWidth="1"/>
-    <col min="2" max="2" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="45.33203125" customWidth="1"/>
-    <col min="8" max="8" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.28515625" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="45.28515625" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -693,7 +693,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -728,17 +728,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A1E03D-541C-4A0E-B2A6-D6E8D094BDAF}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>36</v>
       </c>

--- a/TestData/LV_T2006_GiftLog_GiftRequestProcess_GiftSubmissionForCurrentAndNextCalendarYear.xlsx
+++ b/TestData/LV_T2006_GiftLog_GiftRequestProcess_GiftSubmissionForCurrentAndNextCalendarYear.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23CD10C3-0370-4E75-B851-07B1EBD1AB9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5296B936-2074-4061-B2BB-CCD173CAACEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="5" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
   <si>
     <t>Client Gift Pre-approval</t>
   </si>
@@ -147,6 +147,9 @@
   </si>
   <si>
     <t>Melissa Zatta</t>
+  </si>
+  <si>
+    <t>Julie Carthane</t>
   </si>
 </sst>
 </file>
@@ -480,19 +483,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>38</v>
       </c>
     </row>
@@ -610,7 +617,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>4</v>
